--- a/Employee_Reports_wi48/Shanel Rukshan Perera Kurana Patabendige Q0628.xlsx
+++ b/Employee_Reports_wi48/Shanel Rukshan Perera Kurana Patabendige Q0628.xlsx
@@ -560,11 +560,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -609,11 +609,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -658,11 +658,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -707,11 +707,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -756,11 +756,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -805,11 +805,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -854,11 +854,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -903,11 +903,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -952,11 +952,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1001,11 +1001,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1050,11 +1050,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1099,11 +1099,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1136,11 +1136,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1185,11 +1185,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1235,11 +1235,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1284,11 +1284,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1333,11 +1333,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1382,11 +1382,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1405,9 +1405,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
           <t>06-Jun-2026</t>
@@ -1419,11 +1431,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1468,11 +1480,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1505,11 +1517,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1542,11 +1554,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1591,11 +1603,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1757,7 +1769,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7945</v>
+        <v>7942</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -1780,7 +1792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1852,7 +1864,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7960</v>
+        <v>7957</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -1881,7 +1893,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7960</v>
+        <v>7957</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -1910,7 +1922,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7937</v>
+        <v>7934</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -1939,7 +1951,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7960</v>
+        <v>7957</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -1968,7 +1980,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7960</v>
+        <v>7957</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -1997,7 +2009,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7937</v>
+        <v>7934</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2026,7 +2038,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7982</v>
+        <v>7979</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2055,7 +2067,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7982</v>
+        <v>7979</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2084,7 +2096,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7967</v>
+        <v>7964</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2113,7 +2125,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7967</v>
+        <v>7964</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2133,16 +2145,16 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>25-Jun-2026</t>
+          <t>07-Jul-2026</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>20-May-2048</t>
+          <t>01-Jun-2048</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7982</v>
+        <v>7991</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2162,16 +2174,16 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>25-Jun-2026</t>
+          <t>07-Jul-2026</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>20-May-2048</t>
+          <t>01-Jun-2048</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7982</v>
+        <v>7991</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2191,16 +2203,16 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>25-Jun-2026</t>
+          <t>07-Jul-2026</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>20-May-2048</t>
+          <t>01-Jun-2048</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7982</v>
+        <v>7991</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2220,16 +2232,16 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>25-Jun-2026</t>
+          <t>07-Jul-2026</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>20-May-2048</t>
+          <t>01-Jun-2048</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7982</v>
+        <v>7991</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -2258,7 +2270,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7967</v>
+        <v>7964</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -2287,7 +2299,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7967</v>
+        <v>7964</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -2295,6 +2307,35 @@
         </is>
       </c>
       <c r="G18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>floor scale</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>07-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>01-Jun-2048</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>7991</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
